--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733249</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129733244</v>
       </c>
       <c r="B3" t="n">
-        <v>98685</v>
+        <v>98686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733242</v>
+        <v>129733252</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>98686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544688</v>
+        <v>544850</v>
       </c>
       <c r="R4" t="n">
-        <v>6781720</v>
+        <v>6781806</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733252</v>
+        <v>129733242</v>
       </c>
       <c r="B5" t="n">
-        <v>98685</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544850</v>
+        <v>544688</v>
       </c>
       <c r="R5" t="n">
-        <v>6781806</v>
+        <v>6781720</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1082,7 +1082,7 @@
         <v>129733236</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129733246</v>
       </c>
       <c r="B7" t="n">
-        <v>79099</v>
+        <v>79100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>129733251</v>
       </c>
       <c r="B9" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B10" t="n">
-        <v>98672</v>
+        <v>79108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R10" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B11" t="n">
-        <v>79107</v>
+        <v>98673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R11" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,48 +1690,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733247</v>
+        <v>129733235</v>
       </c>
       <c r="B12" t="n">
-        <v>98789</v>
+        <v>57557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>102976</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Hibo, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544850</v>
+        <v>544695</v>
       </c>
       <c r="R12" t="n">
-        <v>6781806</v>
+        <v>6781758</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1794,7 +1799,7 @@
         <v>129733245</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,53 +1897,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733235</v>
+        <v>129733247</v>
       </c>
       <c r="B14" t="n">
-        <v>57556</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102976</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hibo, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544695</v>
+        <v>544850</v>
       </c>
       <c r="R14" t="n">
-        <v>6781758</v>
+        <v>6781806</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -1281,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>83045</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R8" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,45 +1382,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B9" t="n">
-        <v>83045</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R9" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733249</v>
+        <v>129733244</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>98691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544823</v>
+        <v>544705</v>
       </c>
       <c r="R2" t="n">
-        <v>6781798</v>
+        <v>6781734</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733244</v>
+        <v>129733249</v>
       </c>
       <c r="B3" t="n">
-        <v>98686</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544705</v>
+        <v>544823</v>
       </c>
       <c r="R3" t="n">
-        <v>6781734</v>
+        <v>6781798</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
         <v>129733252</v>
       </c>
       <c r="B4" t="n">
-        <v>98686</v>
+        <v>98691</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129733242</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129733236</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129733246</v>
       </c>
       <c r="B7" t="n">
-        <v>79100</v>
+        <v>79105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,45 +1281,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B8" t="n">
-        <v>83045</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R8" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,50 +1387,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>83050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R9" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,7 +1491,7 @@
         <v>129733149</v>
       </c>
       <c r="B10" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>129733256</v>
       </c>
       <c r="B11" t="n">
-        <v>98673</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,53 +1690,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733235</v>
+        <v>129733245</v>
       </c>
       <c r="B12" t="n">
-        <v>57557</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hibo, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544695</v>
+        <v>544801</v>
       </c>
       <c r="R12" t="n">
-        <v>6781758</v>
+        <v>6781844</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733245</v>
+        <v>129733247</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>98795</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544801</v>
+        <v>544850</v>
       </c>
       <c r="R13" t="n">
-        <v>6781844</v>
+        <v>6781806</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1897,48 +1892,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733247</v>
+        <v>129733235</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>57557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>102976</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Hibo, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544850</v>
+        <v>544695</v>
       </c>
       <c r="R14" t="n">
-        <v>6781806</v>
+        <v>6781758</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733244</v>
+        <v>129733249</v>
       </c>
       <c r="B2" t="n">
-        <v>98691</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544705</v>
+        <v>544823</v>
       </c>
       <c r="R2" t="n">
-        <v>6781734</v>
+        <v>6781798</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733249</v>
+        <v>129733244</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>98691</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544823</v>
+        <v>544705</v>
       </c>
       <c r="R3" t="n">
-        <v>6781798</v>
+        <v>6781734</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733252</v>
+        <v>129733242</v>
       </c>
       <c r="B4" t="n">
-        <v>98691</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544850</v>
+        <v>544688</v>
       </c>
       <c r="R4" t="n">
-        <v>6781806</v>
+        <v>6781720</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733242</v>
+        <v>129733252</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>98691</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544688</v>
+        <v>544850</v>
       </c>
       <c r="R5" t="n">
-        <v>6781720</v>
+        <v>6781806</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1281,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>83050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R8" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,45 +1382,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B9" t="n">
-        <v>83050</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R9" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733249</v>
+        <v>129733244</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>98691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544823</v>
+        <v>544705</v>
       </c>
       <c r="R2" t="n">
-        <v>6781798</v>
+        <v>6781734</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733244</v>
+        <v>129733249</v>
       </c>
       <c r="B3" t="n">
-        <v>98691</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544705</v>
+        <v>544823</v>
       </c>
       <c r="R3" t="n">
-        <v>6781734</v>
+        <v>6781798</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1791,48 +1791,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733247</v>
+        <v>129733235</v>
       </c>
       <c r="B13" t="n">
-        <v>98795</v>
+        <v>57557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>102976</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Hibo, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544850</v>
+        <v>544695</v>
       </c>
       <c r="R13" t="n">
-        <v>6781806</v>
+        <v>6781758</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,53 +1897,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733235</v>
+        <v>129733247</v>
       </c>
       <c r="B14" t="n">
-        <v>57557</v>
+        <v>98795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102976</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hibo, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544695</v>
+        <v>544850</v>
       </c>
       <c r="R14" t="n">
-        <v>6781758</v>
+        <v>6781806</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733244</v>
+        <v>129733249</v>
       </c>
       <c r="B2" t="n">
-        <v>98691</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544705</v>
+        <v>544823</v>
       </c>
       <c r="R2" t="n">
-        <v>6781734</v>
+        <v>6781798</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733249</v>
+        <v>129733244</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>98691</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544823</v>
+        <v>544705</v>
       </c>
       <c r="R3" t="n">
-        <v>6781798</v>
+        <v>6781734</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733242</v>
+        <v>129733252</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>98691</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544688</v>
+        <v>544850</v>
       </c>
       <c r="R4" t="n">
-        <v>6781720</v>
+        <v>6781806</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733252</v>
+        <v>129733242</v>
       </c>
       <c r="B5" t="n">
-        <v>98691</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544850</v>
+        <v>544688</v>
       </c>
       <c r="R5" t="n">
-        <v>6781806</v>
+        <v>6781720</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1281,45 +1281,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B8" t="n">
-        <v>83050</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R8" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,50 +1387,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>83050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R9" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>129733244</v>
       </c>
       <c r="B3" t="n">
-        <v>98691</v>
+        <v>98695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733252</v>
+        <v>129733242</v>
       </c>
       <c r="B4" t="n">
-        <v>98691</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544850</v>
+        <v>544688</v>
       </c>
       <c r="R4" t="n">
-        <v>6781806</v>
+        <v>6781720</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733242</v>
+        <v>129733252</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>98695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544688</v>
+        <v>544850</v>
       </c>
       <c r="R5" t="n">
-        <v>6781720</v>
+        <v>6781806</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B10" t="n">
-        <v>79113</v>
+        <v>98682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R10" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>79113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R11" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,48 +1690,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733245</v>
+        <v>129733235</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>57557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Hibo, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544801</v>
+        <v>544695</v>
       </c>
       <c r="R12" t="n">
-        <v>6781844</v>
+        <v>6781758</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1791,53 +1796,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733235</v>
+        <v>129733245</v>
       </c>
       <c r="B13" t="n">
-        <v>57557</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hibo, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544695</v>
+        <v>544801</v>
       </c>
       <c r="R13" t="n">
-        <v>6781758</v>
+        <v>6781844</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>129733247</v>
       </c>
       <c r="B14" t="n">
-        <v>98795</v>
+        <v>98799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>129733244</v>
       </c>
       <c r="B3" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129733252</v>
       </c>
       <c r="B5" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1281,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>83052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R8" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,45 +1382,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B9" t="n">
-        <v>83050</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R9" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B10" t="n">
-        <v>98682</v>
+        <v>79113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R10" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B11" t="n">
-        <v>79113</v>
+        <v>98684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R11" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,53 +1690,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733235</v>
+        <v>129733245</v>
       </c>
       <c r="B12" t="n">
-        <v>57557</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hibo, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544695</v>
+        <v>544801</v>
       </c>
       <c r="R12" t="n">
-        <v>6781758</v>
+        <v>6781844</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733245</v>
+        <v>129733247</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>98801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544801</v>
+        <v>544850</v>
       </c>
       <c r="R13" t="n">
-        <v>6781844</v>
+        <v>6781806</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1897,48 +1892,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733247</v>
+        <v>129733235</v>
       </c>
       <c r="B14" t="n">
-        <v>98799</v>
+        <v>57557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>102976</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Hibo, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544850</v>
+        <v>544695</v>
       </c>
       <c r="R14" t="n">
-        <v>6781806</v>
+        <v>6781758</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -1690,32 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733245</v>
+        <v>129733247</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>98801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544801</v>
+        <v>544850</v>
       </c>
       <c r="R12" t="n">
-        <v>6781844</v>
+        <v>6781806</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1791,32 +1791,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733247</v>
+        <v>129733245</v>
       </c>
       <c r="B13" t="n">
-        <v>98801</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544850</v>
+        <v>544801</v>
       </c>
       <c r="R13" t="n">
-        <v>6781806</v>
+        <v>6781844</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>129733244</v>
       </c>
       <c r="B3" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129733252</v>
       </c>
       <c r="B5" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1281,45 +1281,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B8" t="n">
-        <v>83052</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R8" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,50 +1387,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>83052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R9" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1592,7 +1592,7 @@
         <v>129733256</v>
       </c>
       <c r="B11" t="n">
-        <v>98684</v>
+        <v>98694</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,32 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733247</v>
+        <v>129733245</v>
       </c>
       <c r="B12" t="n">
-        <v>98801</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544850</v>
+        <v>544801</v>
       </c>
       <c r="R12" t="n">
-        <v>6781806</v>
+        <v>6781844</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1791,48 +1791,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733245</v>
+        <v>129733235</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Hibo, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544801</v>
+        <v>544695</v>
       </c>
       <c r="R13" t="n">
-        <v>6781844</v>
+        <v>6781758</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,53 +1897,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733235</v>
+        <v>129733247</v>
       </c>
       <c r="B14" t="n">
-        <v>57557</v>
+        <v>98811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102976</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hibo, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544695</v>
+        <v>544850</v>
       </c>
       <c r="R14" t="n">
-        <v>6781758</v>
+        <v>6781806</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -1281,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>83052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R8" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,45 +1382,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B9" t="n">
-        <v>83052</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R9" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B10" t="n">
-        <v>79113</v>
+        <v>98694</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R10" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B11" t="n">
-        <v>98694</v>
+        <v>79113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R11" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733249</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129733244</v>
       </c>
       <c r="B3" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129733242</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129733252</v>
       </c>
       <c r="B5" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129733236</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129733246</v>
       </c>
       <c r="B7" t="n">
-        <v>79105</v>
+        <v>79108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,45 +1281,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B8" t="n">
-        <v>83052</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R8" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,50 +1387,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>83055</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R9" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,7 +1491,7 @@
         <v>129733256</v>
       </c>
       <c r="B10" t="n">
-        <v>98694</v>
+        <v>98698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>129733149</v>
       </c>
       <c r="B11" t="n">
-        <v>79113</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>129733245</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>129733235</v>
       </c>
       <c r="B13" t="n">
-        <v>57557</v>
+        <v>57558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>129733247</v>
       </c>
       <c r="B14" t="n">
-        <v>98811</v>
+        <v>98815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733242</v>
+        <v>129733252</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>98711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544688</v>
+        <v>544850</v>
       </c>
       <c r="R4" t="n">
-        <v>6781720</v>
+        <v>6781806</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733252</v>
+        <v>129733242</v>
       </c>
       <c r="B5" t="n">
-        <v>98711</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544850</v>
+        <v>544688</v>
       </c>
       <c r="R5" t="n">
-        <v>6781806</v>
+        <v>6781720</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1281,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>83055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R8" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,45 +1382,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B9" t="n">
-        <v>83055</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R9" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B10" t="n">
-        <v>98698</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R10" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>98698</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R11" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,32 +1690,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733245</v>
+        <v>129733247</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>98815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544801</v>
+        <v>544850</v>
       </c>
       <c r="R12" t="n">
-        <v>6781844</v>
+        <v>6781806</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1791,53 +1791,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733235</v>
+        <v>129733245</v>
       </c>
       <c r="B13" t="n">
-        <v>57558</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hibo, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544695</v>
+        <v>544801</v>
       </c>
       <c r="R13" t="n">
-        <v>6781758</v>
+        <v>6781844</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,48 +1892,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733247</v>
+        <v>129733235</v>
       </c>
       <c r="B14" t="n">
-        <v>98815</v>
+        <v>57558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>102976</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Hibo, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544850</v>
+        <v>544695</v>
       </c>
       <c r="R14" t="n">
-        <v>6781806</v>
+        <v>6781758</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>98698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R10" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B11" t="n">
-        <v>98698</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R11" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733249</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129733244</v>
       </c>
       <c r="B3" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733252</v>
+        <v>129733242</v>
       </c>
       <c r="B4" t="n">
-        <v>98711</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544850</v>
+        <v>544688</v>
       </c>
       <c r="R4" t="n">
-        <v>6781806</v>
+        <v>6781720</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733242</v>
+        <v>129733252</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>98714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544688</v>
+        <v>544850</v>
       </c>
       <c r="R5" t="n">
-        <v>6781720</v>
+        <v>6781806</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1082,7 +1082,7 @@
         <v>129733236</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129733246</v>
       </c>
       <c r="B7" t="n">
-        <v>79108</v>
+        <v>79111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,45 +1281,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B8" t="n">
-        <v>83055</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R8" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,50 +1387,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B9" t="n">
-        <v>5197</v>
+        <v>83058</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R9" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B10" t="n">
-        <v>98698</v>
+        <v>79119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R10" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>98701</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R11" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,48 +1690,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733247</v>
+        <v>129733235</v>
       </c>
       <c r="B12" t="n">
-        <v>98815</v>
+        <v>57561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>102976</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Hibo, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544850</v>
+        <v>544695</v>
       </c>
       <c r="R12" t="n">
-        <v>6781806</v>
+        <v>6781758</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1791,32 +1796,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733245</v>
+        <v>129733247</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>98818</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544801</v>
+        <v>544850</v>
       </c>
       <c r="R13" t="n">
-        <v>6781844</v>
+        <v>6781806</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1892,53 +1897,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733235</v>
+        <v>129733245</v>
       </c>
       <c r="B14" t="n">
-        <v>57558</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hibo, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544695</v>
+        <v>544801</v>
       </c>
       <c r="R14" t="n">
-        <v>6781758</v>
+        <v>6781844</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733249</v>
+        <v>129733244</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>98714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544823</v>
+        <v>544705</v>
       </c>
       <c r="R2" t="n">
-        <v>6781798</v>
+        <v>6781734</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733244</v>
+        <v>129733249</v>
       </c>
       <c r="B3" t="n">
-        <v>98714</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544705</v>
+        <v>544823</v>
       </c>
       <c r="R3" t="n">
-        <v>6781734</v>
+        <v>6781798</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1796,32 +1796,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733247</v>
+        <v>129733245</v>
       </c>
       <c r="B13" t="n">
-        <v>98818</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544850</v>
+        <v>544801</v>
       </c>
       <c r="R13" t="n">
-        <v>6781806</v>
+        <v>6781844</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1897,32 +1897,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733245</v>
+        <v>129733247</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>98818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544801</v>
+        <v>544850</v>
       </c>
       <c r="R14" t="n">
-        <v>6781844</v>
+        <v>6781806</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733244</v>
+        <v>129733249</v>
       </c>
       <c r="B2" t="n">
-        <v>98714</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544705</v>
+        <v>544823</v>
       </c>
       <c r="R2" t="n">
-        <v>6781734</v>
+        <v>6781798</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733249</v>
+        <v>129733244</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>98715</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544823</v>
+        <v>544705</v>
       </c>
       <c r="R3" t="n">
-        <v>6781798</v>
+        <v>6781734</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
         <v>129733242</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129733252</v>
       </c>
       <c r="B5" t="n">
-        <v>98714</v>
+        <v>98715</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129733236</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129733246</v>
       </c>
       <c r="B7" t="n">
-        <v>79111</v>
+        <v>79112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>129733251</v>
       </c>
       <c r="B9" t="n">
-        <v>83058</v>
+        <v>83059</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B10" t="n">
-        <v>79119</v>
+        <v>98702</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R10" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B11" t="n">
-        <v>98701</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R11" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>129733245</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>129733247</v>
       </c>
       <c r="B14" t="n">
-        <v>98818</v>
+        <v>98819</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B10" t="n">
-        <v>98702</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R10" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>98702</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R11" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>98702</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R10" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B11" t="n">
-        <v>98702</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R11" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2024 artfynd.xlsx
+++ b/artfynd/A 19656-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733249</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129733244</v>
       </c>
       <c r="B3" t="n">
-        <v>98715</v>
+        <v>98732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129733242</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>129733252</v>
       </c>
       <c r="B5" t="n">
-        <v>98715</v>
+        <v>98732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129733236</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129733246</v>
       </c>
       <c r="B7" t="n">
-        <v>79112</v>
+        <v>79113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733233</v>
+        <v>129733251</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>83065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skålsjöberget, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544669</v>
+        <v>544842</v>
       </c>
       <c r="R8" t="n">
-        <v>6781701</v>
+        <v>6781804</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,45 +1382,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733251</v>
+        <v>129733233</v>
       </c>
       <c r="B9" t="n">
-        <v>83059</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Skålsjöberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544842</v>
+        <v>544669</v>
       </c>
       <c r="R9" t="n">
-        <v>6781804</v>
+        <v>6781701</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733256</v>
+        <v>129733149</v>
       </c>
       <c r="B10" t="n">
-        <v>98702</v>
+        <v>79121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544868</v>
+        <v>544730</v>
       </c>
       <c r="R10" t="n">
-        <v>6781819</v>
+        <v>6781692</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733149</v>
+        <v>129733256</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>98719</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544730</v>
+        <v>544868</v>
       </c>
       <c r="R11" t="n">
-        <v>6781692</v>
+        <v>6781819</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,53 +1690,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733235</v>
+        <v>129733245</v>
       </c>
       <c r="B12" t="n">
-        <v>57561</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hibo, Hls</t>
+          <t>Österberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544695</v>
+        <v>544801</v>
       </c>
       <c r="R12" t="n">
-        <v>6781758</v>
+        <v>6781844</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,48 +1791,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733245</v>
+        <v>129733235</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>57561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Österberget, Hls</t>
+          <t>Hibo, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544801</v>
+        <v>544695</v>
       </c>
       <c r="R13" t="n">
-        <v>6781844</v>
+        <v>6781758</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>129733247</v>
       </c>
       <c r="B14" t="n">
-        <v>98819</v>
+        <v>98836</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
